--- a/artfynd/S 1487-2025 artfynd.xlsx
+++ b/artfynd/S 1487-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2286,62 +2286,61 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>53335946</v>
+        <v>135140997</v>
       </c>
       <c r="B17" t="n">
-        <v>8444</v>
+        <v>45050</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>102018</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Berga Fly, Sm</t>
+          <t>Bergavägen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529737</v>
+        <v>528658</v>
       </c>
       <c r="R17" t="n">
-        <v>6330127</v>
+        <v>6330703</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2365,12 +2364,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2014-07-14</t>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2014-08-04</t>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2379,68 +2393,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Barrskogsbränna</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>bränd tall</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # bränd tall</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>Gunnar Sjödin</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
+      <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Sjödin</t>
+          <t>thorsten Zaar</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Sjödin</t>
+          <t>thorsten Zaar</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126194671</v>
+        <v>53335946</v>
       </c>
       <c r="B18" t="n">
-        <v>58461</v>
+        <v>8444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103018</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2470,35 +2445,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fönsterfälla</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björkå, Åkvarn, Sm</t>
+          <t>Berga Fly, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533656</v>
+        <v>529737</v>
       </c>
       <c r="R18" t="n">
-        <v>6329324</v>
+        <v>6330127</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2517,27 +2486,17 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Älghult</t>
+          <t>Åseda</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>07:05</t>
+          <t>2014-07-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>07:05</t>
+          <t>2014-08-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2549,25 +2508,65 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AT18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Barrskogsbränna</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>bränd tall</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # bränd tall</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>Gunnar Sjödin</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Per Tengroth</t>
+          <t>Erik Sjödin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Per Tengroth</t>
+          <t>Erik Sjödin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89326742</v>
+        <v>126194671</v>
       </c>
       <c r="B19" t="n">
-        <v>57141</v>
+        <v>58461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2575,21 +2574,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>103018</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2597,19 +2596,35 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Landskapet kring Hökasjön, Sm</t>
+          <t>Björkå, Åkvarn, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530377</v>
+        <v>533656</v>
       </c>
       <c r="R19" t="n">
-        <v>6329114</v>
+        <v>6329324</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2628,17 +2643,27 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Åseda</t>
+          <t>Älghult</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2020-05-06</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>07:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>07:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2653,22 +2678,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Per Tengroth</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Per Tengroth</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89326724</v>
+        <v>89326742</v>
       </c>
       <c r="B20" t="n">
-        <v>97983</v>
+        <v>57141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2676,34 +2701,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Landskapet kring Hökasjön, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>531306</v>
+        <v>530377</v>
       </c>
       <c r="R20" t="n">
-        <v>6329593</v>
+        <v>6329114</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2762,10 +2791,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89736815</v>
+        <v>89326724</v>
       </c>
       <c r="B21" t="n">
-        <v>56835</v>
+        <v>97983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2773,51 +2802,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205995</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hökanäs-Hovgård Boxplats 5, Sm</t>
+          <t>Landskapet kring Hökasjön, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>531394</v>
+        <v>531306</v>
       </c>
       <c r="R21" t="n">
-        <v>6327038</v>
+        <v>6329593</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2841,22 +2856,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>20:00</t>
+          <t>2020-05-06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:30</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2871,49 +2876,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>89736814</v>
+        <v>89736815</v>
       </c>
       <c r="B22" t="n">
-        <v>56816</v>
+        <v>56835</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3004,48 +3009,62 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>89326898</v>
+        <v>89736814</v>
       </c>
       <c r="B23" t="n">
-        <v>96708</v>
+        <v>56816</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>205998</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Landskapet kring Hökasjön, Sm</t>
+          <t>Hökanäs-Hovgård Boxplats 5, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>531670</v>
+        <v>531394</v>
       </c>
       <c r="R23" t="n">
-        <v>6329352</v>
+        <v>6327038</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3069,12 +3088,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-05-06</t>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2020-09-16</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>00:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3089,22 +3118,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Petter Bohman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Petter Bohman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89326897</v>
+        <v>89326898</v>
       </c>
       <c r="B24" t="n">
-        <v>97986</v>
+        <v>96708</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3112,21 +3141,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221946</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3136,10 +3165,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>531567</v>
+        <v>531670</v>
       </c>
       <c r="R24" t="n">
-        <v>6330317</v>
+        <v>6329352</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3198,10 +3227,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>57927054</v>
+        <v>89326897</v>
       </c>
       <c r="B25" t="n">
-        <v>57141</v>
+        <v>97986</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3209,56 +3238,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>221946</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kåreskruv, Sm</t>
+          <t>Landskapet kring Hökasjön, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532761</v>
+        <v>531567</v>
       </c>
       <c r="R25" t="n">
-        <v>6328454</v>
+        <v>6330317</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3282,22 +3292,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2016-03-30</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2020-05-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2016-03-30</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3312,60 +3312,79 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lisa Petersson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lisa Petersson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>74439839</v>
+        <v>57927054</v>
       </c>
       <c r="B26" t="n">
-        <v>104159</v>
+        <v>57141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>706</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Geranium bohemicum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nyelund 750 m NNO, Sm</t>
+          <t>Kåreskruv, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532230</v>
+        <v>532761</v>
       </c>
       <c r="R26" t="n">
-        <v>6329542</v>
+        <v>6328454</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3389,17 +3408,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>1995-10-12</t>
+          <t>2016-03-30</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>1995-10-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 5F6g 1334. SOM: Geranium bohemicum. LEG: Kerstin Petersson. KOM: 20 plantor</t>
+          <t>2016-03-30</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3410,73 +3434,64 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Brandfält 1994, tallplantering</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Lisa Petersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Lisa Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89326901</v>
+        <v>74439839</v>
       </c>
       <c r="B27" t="n">
-        <v>97733</v>
+        <v>104159</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2569</v>
+        <v>706</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Geranium bohemicum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Landskapet kring Hökasjön, Sm</t>
+          <t>Nyelund 750 m NNO, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>532329</v>
+        <v>532230</v>
       </c>
       <c r="R27" t="n">
-        <v>6330103</v>
+        <v>6329542</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3500,12 +3515,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2020-05-06</t>
+          <t>1995-10-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>1995-10-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 5F6g 1334. SOM: Geranium bohemicum. LEG: Kerstin Petersson. KOM: 20 plantor</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3516,48 +3536,57 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Brandfält 1994, tallplantering</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>89326900</v>
+        <v>89326901</v>
       </c>
       <c r="B28" t="n">
-        <v>79946</v>
+        <v>97733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>2569</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3567,10 +3596,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>532360</v>
+        <v>532329</v>
       </c>
       <c r="R28" t="n">
-        <v>6329899</v>
+        <v>6330103</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3626,6 +3655,103 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>89326900</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Landskapet kring Hökasjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>532360</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6329899</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Åseda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2020-05-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2020-05-15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
